--- a/UNIDAD 1/G2_Matriz_IREB_V3.0.xlsx
+++ b/UNIDAD 1/G2_Matriz_IREB_V3.0.xlsx
@@ -22,22 +22,23 @@
     <author/>
   </authors>
   <commentList>
-    <comment authorId="0" ref="G7">
-      <text>
-        <t xml:space="preserve">jeny ruiz:
-Control del nivel de acuedo entre las partes Cliente y Desarrollador</t>
-      </text>
-    </comment>
     <comment authorId="0" ref="I9">
       <text>
         <t xml:space="preserve">jeny ruiz:
 Es importante ingresar el archivo plano en formato excel para el cliente y el desarrollador</t>
       </text>
     </comment>
-    <comment authorId="0" ref="I7">
+    <comment authorId="0" ref="C67">
       <text>
         <t xml:space="preserve">jeny ruiz:
-Se guarda en un archivo Excel los registros que dieron un problema en la actualización.</t>
+Trata todos los asuntos relevantes</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="C34">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Sin contradicciones
+</t>
       </text>
     </comment>
     <comment authorId="0" ref="K9">
@@ -46,23 +47,29 @@
 Es importante ingresar el archivo plano en formato excel para el cliente y el desarrollador</t>
       </text>
     </comment>
-    <comment authorId="0" ref="J7">
+    <comment authorId="0" ref="C63">
       <text>
         <t xml:space="preserve">jeny ruiz:
-Control del nivel de acuedo entre las partes Cliente y Desarrollador</t>
+Sin contradicciones
+</t>
       </text>
     </comment>
-    <comment authorId="0" ref="K7">
+    <comment authorId="0" ref="C30">
       <text>
         <t xml:space="preserve">jeny ruiz:
-jeny ruiz:
-Posterior a la actualización, se guardaran automáticamente el nombre de usuario, fecha, hora, registro antiguo, registro nuevo.</t>
+Ponderado por importancia o prioridad</t>
       </text>
     </comment>
-    <comment authorId="0" ref="C19">
+    <comment authorId="0" ref="C59">
       <text>
         <t xml:space="preserve">jeny ruiz:
-Para todos los interesados dependiendo  de la fase del proyecto podrían estar involucrados  distintos implicados,(Glosario de tèrminos)</t>
+Ponderado por importancia o prioridad</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="C51">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Puede ser implementado  y desarrollado en las condiciones actuales(tiempo, Presupuest,, orgtanizaciòn, ect)</t>
       </text>
     </comment>
     <comment authorId="0" ref="C18">
@@ -71,22 +78,10 @@
 Trata todos los asuntos relevantes</t>
       </text>
     </comment>
-    <comment authorId="0" ref="C17">
+    <comment authorId="0" ref="C47">
       <text>
         <t xml:space="preserve">jeny ruiz:
-El origen del requisito y sus relaciones con otros requisitos  están claros.</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="C16">
-      <text>
-        <t xml:space="preserve">jeny ruiz:
-Puede ser implementado  y desarrollado en las condiciones actuales(tiempo, Presupuest,, orgtanizaciòn, ect)</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="C15">
-      <text>
-        <t xml:space="preserve">jeny ruiz:
-Su cumplimiento o no cumplimiento puede der probado con un esfuerzo razonable</t>
+Toda nueva información  ha sido incorporada</t>
       </text>
     </comment>
     <comment authorId="0" ref="C14">
@@ -96,17 +91,103 @@
 </t>
       </text>
     </comment>
-    <comment authorId="0" ref="C13">
+    <comment authorId="0" ref="C10">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Ponderado por importancia o prioridad</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="C39">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Para todos los interesados dependiendo  de la fase del proyecto podrían estar involucrados  distintos implicados,(Glosario de tèrminos)</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="C68">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Para todos los interesados dependiendo  de la fase del proyecto podrían estar involucrados  distintos implicados,(Glosario de tèrminos)</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="C35">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Su cumplimiento o no cumplimiento puede der probado con un esfuerzo razonable</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="C64">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Su cumplimiento o no cumplimiento puede der probado con un esfuerzo razonable</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="C31">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Todos los lectores comprenden de la misma manera, sólo una interpretación</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="C60">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Todos los lectores comprenden de la misma manera, sólo una interpretación</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="E27">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Control del nivel de acuedo entre las partes Cliente y Desarrollador</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="F27">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+La información contenida en memoria se utiliza para actualizar los campos de la base de datos.</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="E56">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Control del nivel de acuedo entre las partes Cliente y Desarrollador</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="F56">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+jeny ruiz:
+Posterior a la actualización, se guardaran automáticamente el nombre de usuario, fecha, hora, registro antiguo, registro nuevo.</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="C52">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+El origen del requisito y sus relaciones con otros requisitos  están claros.</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="C19">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Para todos los interesados dependiendo  de la fase del proyecto podrían estar involucrados  distintos implicados,(Glosario de tèrminos)</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="C48">
       <text>
         <t xml:space="preserve">jeny ruiz:
 Refleja las espectativas  del implicado
 </t>
       </text>
     </comment>
-    <comment authorId="0" ref="C12">
+    <comment authorId="0" ref="C15">
       <text>
         <t xml:space="preserve">jeny ruiz:
-Toda nueva información  ha sido incorporada</t>
+Su cumplimiento o no cumplimiento puede der probado con un esfuerzo razonable</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="C44">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Todos los interesados reconocen que el  requisito es correcto y relevante
+</t>
       </text>
     </comment>
     <comment authorId="0" ref="C11">
@@ -115,20 +196,13 @@
 Todos los lectores comprenden de la misma manera, sólo una interpretación</t>
       </text>
     </comment>
-    <comment authorId="0" ref="C10">
+    <comment authorId="0" ref="F44">
       <text>
         <t xml:space="preserve">jeny ruiz:
-Ponderado por importancia o prioridad</t>
+Es importante ingresar el archivo plano en formato excel para el cliente y el desarrollador</t>
       </text>
     </comment>
-    <comment authorId="0" ref="C9">
-      <text>
-        <t xml:space="preserve">jeny ruiz:
-Todos los interesados reconocen que el  requisito es correcto y relevante
-</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="F9">
+    <comment authorId="0" ref="G44">
       <text>
         <t xml:space="preserve">jeny ruiz:
 Es importante ingresar el archivo plano en formato excel para el cliente y el desarrollador</t>
@@ -144,6 +218,206 @@
       <text>
         <t xml:space="preserve">jeny ruiz:
 La información contenida en memoria se utiliza para actualizar los campos de la base de datos.</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="C36">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Puede ser implementado  y desarrollado en las condiciones actuales(tiempo, Presupuest,, orgtanizaciòn, ect)</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="G7">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Control del nivel de acuedo entre las partes Cliente y Desarrollador</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="I7">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Se guarda en un archivo Excel los registros que dieron un problema en la actualización.</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="C65">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Puede ser implementado  y desarrollado en las condiciones actuales(tiempo, Presupuest,, orgtanizaciòn, ect)</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="J7">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Control del nivel de acuedo entre las partes Cliente y Desarrollador</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="C32">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Toda nueva información  ha sido incorporada</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="K7">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+jeny ruiz:
+Posterior a la actualización, se guardaran automáticamente el nombre de usuario, fecha, hora, registro antiguo, registro nuevo.</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="C61">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Toda nueva información  ha sido incorporada</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="C53">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Trata todos los asuntos relevantes</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="C49">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Sin contradicciones
+</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="C16">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Puede ser implementado  y desarrollado en las condiciones actuales(tiempo, Presupuest,, orgtanizaciòn, ect)</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="C45">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Ponderado por importancia o prioridad</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="C12">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Toda nueva información  ha sido incorporada</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="C37">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+El origen del requisito y sus relaciones con otros requisitos  están claros.</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="C66">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+El origen del requisito y sus relaciones con otros requisitos  están claros.</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="C33">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Refleja las espectativas  del implicado
+</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="C62">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Refleja las espectativas  del implicado
+</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="C29">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Todos los interesados reconocen que el  requisito es correcto y relevante
+</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="F29">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Es importante ingresar el archivo plano en formato excel para el cliente y el desarrollador</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="C58">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Todos los interesados reconocen que el  requisito es correcto y relevante
+</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="F58">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Es importante ingresar el archivo plano en formato excel para el cliente y el desarrollador</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="C54">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Para todos los interesados dependiendo  de la fase del proyecto podrían estar involucrados  distintos implicados,(Glosario de tèrminos)</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="C50">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Su cumplimiento o no cumplimiento puede der probado con un esfuerzo razonable</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="C17">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+El origen del requisito y sus relaciones con otros requisitos  están claros.</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="C46">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Todos los lectores comprenden de la misma manera, sólo una interpretación</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="C13">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Refleja las espectativas  del implicado
+</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="C9">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Todos los interesados reconocen que el  requisito es correcto y relevante
+</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="E42">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Control del nivel de acuedo entre las partes Cliente y Desarrollador</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="F42">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Se guarda en un archivo Excel los registros que dieron un problema en la actualización.</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="F9">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Es importante ingresar el archivo plano en formato excel para el cliente y el desarrollador</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="C38">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Trata todos los asuntos relevantes</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="G42">
+      <text>
+        <t xml:space="preserve">jeny ruiz:
+Se guarda en un archivo Excel los registros que dieron un problema en la actualización.</t>
       </text>
     </comment>
   </commentList>
@@ -361,7 +635,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="108">
   <si>
     <t>MATRIZ PARA COMPROBACIÓN REQUERIMIENTOS DE CALIDAD DE PROYECTO ACADEMICO</t>
   </si>
@@ -417,13 +691,13 @@
     <t xml:space="preserve">1.  Redacción en lenguaje claro.                                                                               2. El tutor y el equipo interpretan de igual manera el caso de uso </t>
   </si>
   <si>
-    <t>NOK</t>
-  </si>
-  <si>
     <t>Valid and up-to date</t>
   </si>
   <si>
     <t>1. Toda nueva información ha sido incorporada, se han incorporado los últimos cambios pedidos luego del feedback realizado por el cliente</t>
+  </si>
+  <si>
+    <t>NOK</t>
   </si>
   <si>
     <t>1. No se han incorporado los últimos cambios pedidos luego del feedback realizado por el cliente</t>
@@ -496,7 +770,7 @@
 2.Uso de términos respaldado por un glosario de términos</t>
   </si>
   <si>
-    <t>Sistema de Gestión de Aforo)</t>
+    <t xml:space="preserve">Sistema De Gestion de aforo </t>
   </si>
   <si>
     <t>FECHA:</t>
@@ -505,10 +779,13 @@
     <t>AUTOR:</t>
   </si>
   <si>
-    <t>Mateo Venegas, Damían Toscano, Josué Guayasamín</t>
+    <t>Josue Chango</t>
   </si>
   <si>
     <t>REQUERIMIENTOS EVALUADOS :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RF2 Monitoreo del aforo en tiempo real </t>
   </si>
   <si>
     <t>CONTENIDO</t>
@@ -550,6 +827,9 @@
     <t>No hay contradicciones entre los requerimientos?</t>
   </si>
   <si>
+    <t xml:space="preserve">            x</t>
+  </si>
+  <si>
     <t>El requerimiento que se esta especificando contribuye a alcanzar un objetivo definido ?</t>
   </si>
   <si>
@@ -586,10 +866,25 @@
     <t>Todos los requerimientos  han sido acordados con todos los interesados?</t>
   </si>
   <si>
+    <t>x</t>
+  </si>
+  <si>
     <t>Todos los requerimientos  modificados han sido acordados por todos los implicados?</t>
   </si>
   <si>
     <t>Han sido resueltos todos los conflictos conocidos respectos de los requerimientos?</t>
+  </si>
+  <si>
+    <t>RESUMEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTENIDO </t>
+  </si>
+  <si>
+    <t>Sistema de Gestión de Aforo)</t>
+  </si>
+  <si>
+    <t>Enrique Ortega</t>
   </si>
   <si>
     <t>PREGUNTA</t>
@@ -598,31 +893,25 @@
     <t>RECOMENDACIÓN</t>
   </si>
   <si>
-    <t>¿Se han validado y aprobado formalmente todos los entregables de la entrevista (videoconferencia, minuta, acta de aceptación)?</t>
+    <t>¿Se ejecutan revisiones constantes del modelo lógico y se actualiza la matriz de trazabilidad para evitar contradicciones operativas?</t>
   </si>
   <si>
-    <t>Se sugiere generar y documentar formalmente la firma de un Acta de Aceptación por parte de los stakeholders principales como es el Gerente General.</t>
+    <t>Se recomienda ejecutar revisiones constantes del modelo lógico y mantener la matriz de trazabilidad para evitar las contradicciones operativas.</t>
   </si>
   <si>
-    <t>RESUMEN</t>
+    <t>¿Se ha implementado un plan de aseguramiento de calidad que incluya hitos técnicos precisos y recursos financieros preasignados para verificar la implementación?</t>
   </si>
   <si>
-    <t>¿Se han definido criterios de aceptación y casos de prueba
- que permitan medir objetivamente el cumplimiento del 
-requisito?</t>
+    <t>Se sugiere implentar un plan de aseguramiento de calidad con hitos técnicos precisos y recursos financieros preasignados para verificar la implementación.</t>
   </si>
   <si>
-    <t>Se recomienda trasladar la sólida base de Criterios de Aceptación actuales hacia un Plan de Pruebas formal que contenga los "Casos de Prueba" detallados paso a paso para el equipo de Aseguramiento de Calidad manteniendo la trazabilidad.</t>
+    <t>¿Se ha redactado y firmado un acta de aceptación con los interesados para formalizar el alcance del proyecto?</t>
   </si>
   <si>
-    <t xml:space="preserve">CONTENIDO </t>
+    <t>Se sugiere escribir un acta de aceptación con los interesados para formalizar el alcance del proyecto.</t>
   </si>
   <si>
-    <t>¿Los valores y metodos de los parametros de conteo estan cerrados o quedan abiertos a
-    interpretacion (criterio Unambiguous)?</t>
-  </si>
-  <si>
-    <t>Se recomienda sustituir el metodo abierto por un metodo unico y obligatorio, y fijar un valor por defecto explicito para el umbral de Salida Inferida dentro del rango de 3 a 4 horas, dejando el rango solo como margen de configuracion</t>
+    <t xml:space="preserve">                                         x</t>
   </si>
   <si>
     <t>¿Existe control de versiones e historial de cambios del documento?</t>
@@ -635,6 +924,9 @@
   </si>
   <si>
     <t>Se recomienda realizar sesiones de validación y consenso con todos los interesados clave antes de cerrar la especificación de requerimientos, esto asegurará que los requerimientos reflejen las necesidades puntuales.</t>
+  </si>
+  <si>
+    <t>Josué Guayasamín</t>
   </si>
   <si>
     <t xml:space="preserve">¿Se ha estimado el esfuerzo, el costo y el plazo necesarios para realizar RF-1.1 a RF-1.10
@@ -659,38 +951,35 @@
     <t>Se recomienda agregar a cada requisito una tabla de precondiciones y postcondiciones, con los estados validos y el esquema de la entidad de sesion de aforo</t>
   </si>
   <si>
-    <t>¿Se ha incorporado los cambios sugeridos por el tutor o el cliente?</t>
+    <t>¿Qué conflicto técnico se identificó entre los disparadores de notificaciones (`RF-3.1`, `RF-3.2`, `RF-3.3`) al ser parametrizables por el administrador, y cómo debemos evitarlo?</t>
   </si>
   <si>
-    <t>Se recomienda establecer un proceso formal de gestión de cambios que incluya el registro, revisión e incorporación de cada sugerencia recibida por parte del tutor o cliente, asegurando que los requisitos estén siempre actualizados, reflejen las expectativas reales y eviten ambigüedades o malentendidos en etapas posteriores del desarrollo.</t>
+    <t>Debemos implementar validaciones lógicas en la interfaz web de parametrización (RF-8.2) que impidan físicamente al Gerente guardar un umbral de descongestión que sea mayor o igual al umbral de saturación u horas pico. De esta forma, evitamos que configuraciones erróneas del usuario generen bucles o notificaciones contradictorias en el servidor.</t>
   </si>
   <si>
-    <t>¿Se mantiene la coherencia con otros requisitos del sistema y utiliza términos o definiciones de forma uniforme a lo largo del documento?</t>
+    <t>¿Qué omisión de estructura cometimos en la documentación de la regla anti-spam (`RF-3.4`) y la sugerencia de horarios (`RF-3.5`), y cómo debemos corregirla?</t>
   </si>
   <si>
-    <t>Aunque el requisito mantiene coherencia con los demás y utiliza los términos de forma uniforme, se recomienda revisar la redacción para eliminar palabras redundantes que no aportan valor, donde una redacción más concisa mejora la claridad del requisito.</t>
+    <t>Debemos  redactar e incorporar formalmente en el SRS los Criterios de Aceptación en formato Dado / Cuando / Entonces (Given / When / Then) para `RF-3.4` (verificando el límite de máximo 2 notificaciones/día con espacio de 2 horas) y `RF-3.5`. Ningún requisito del Módulo 3 debe quedar solo con descripción narrativa.</t>
   </si>
   <si>
-    <t>¿Se han definido casos de prueba que permitan verificar, de manera objetiva y medible, el cumplimiento del requisito?</t>
+    <t>¿Qué ambigüedad semántica o matemática existe entre la descripción de la notificación de afluencia (`RF-3.1`) y su criterio de aceptación `CA-01`?</t>
   </si>
   <si>
-    <t>Se recomienda elaborar casos de prueba específicos para cada requisito, de forma que su cumplimiento pueda ser verificado objetivamente, permitiendo validar que el sistema cumple con lo solicitado y reducirá el riesgo de errores o malentendidos durante el desarrollo y las pruebas.</t>
+    <t>Debemos estandarizar la regla matemática de disparo en todo el documento, decidiéndonos por una sola expresión (`≥ 80%` o &gt; 80%`). Es necesario corregir el texto para que tanto la descripción narrativa como el escenario de prueba utilicen exactamente la misma condición sin margen de duda para el programador o el tester.</t>
   </si>
   <si>
-    <t>¿Todos los requerimientos  han sido acordados con todos los interesados?</t>
+    <t>¿Qué riesgo de aceptación existe al haber diseñado la frecuencia de notificaciones push sin consultar directamente el nivel de tolerancia de los socios del gimnasio?</t>
   </si>
   <si>
-    <t xml:space="preserve">Sistema De Gestion de aforo </t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF2 Monitoreo del aforo en tiempo real </t>
+    <t>Debemos añadir en la App Móvil una pantalla de preferencias de notificación (canales  opt-in / opt-out ) para que el cliente tenga el control de activar o desactivar las alertas proactivas, y realizar una prueba piloto (User Acceptance Testing) con un grupo reducido de socios para medir la tasa de rechazo antes del lanzamiento masivo.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -763,6 +1052,11 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="14.0"/>
       <color theme="1"/>
@@ -786,7 +1080,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -813,14 +1107,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF93C47D"/>
+        <bgColor rgb="FF93C47D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
         <bgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF93C47D"/>
-        <bgColor rgb="FF93C47D"/>
+        <fgColor theme="6"/>
+        <bgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB6D7A8"/>
+        <bgColor rgb="FFB6D7A8"/>
       </patternFill>
     </fill>
     <fill>
@@ -1001,7 +1307,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="69">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1064,46 +1370,50 @@
     <xf borderId="7" fillId="5" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="7" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="7" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="7" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="7" fillId="7" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="13" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="7" fillId="5" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="14" numFmtId="15" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="15" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="12" fillId="7" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="7" fillId="8" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="12" fillId="9" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="14" fillId="7" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="14" fillId="9" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="15" fillId="7" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="15" fillId="9" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1118,6 +1428,12 @@
     <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="6" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -1127,18 +1443,18 @@
     <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="9" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="16" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="16" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="16" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="10" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="10" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="8" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="8" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1150,35 +1466,32 @@
     <xf borderId="5" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="7" fillId="8" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="7" fillId="10" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
+    <xf borderId="7" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
+      <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1367,6 +1680,24 @@
     </dxf>
   </dxfs>
   <tableStyles count="9">
+    <tableStyle count="4" pivot="0" name="MODELO LISTA DE COMPROBACION 2-style">
+      <tableStyleElement dxfId="1" type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    </tableStyle>
+    <tableStyle count="4" pivot="0" name="MODELO LISTA DE COMPROBACION 2-style 2">
+      <tableStyleElement dxfId="5" type="headerRow"/>
+      <tableStyleElement dxfId="6" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+      <tableStyleElement dxfId="7" size="0" type="wholeTable"/>
+    </tableStyle>
+    <tableStyle count="4" pivot="0" name="MODELO LISTA DE COMPROBACION 2-style 3">
+      <tableStyleElement dxfId="8" type="headerRow"/>
+      <tableStyleElement dxfId="9" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+      <tableStyleElement dxfId="10" size="0" type="wholeTable"/>
+    </tableStyle>
     <tableStyle count="4" pivot="0" name="MODELO LISTA DE COMPROBACION 1 -style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
@@ -1391,31 +1722,13 @@
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
       <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
     </tableStyle>
-    <tableStyle count="4" pivot="0" name="MODELO LISTA DE COMPROBACION 2-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
-    </tableStyle>
     <tableStyle count="4" pivot="0" name="MODELO DE LISTA DE COMPROBACION-style 2">
       <tableStyleElement dxfId="5" type="headerRow"/>
       <tableStyleElement dxfId="6" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
       <tableStyleElement dxfId="7" size="0" type="wholeTable"/>
     </tableStyle>
-    <tableStyle count="4" pivot="0" name="MODELO LISTA DE COMPROBACION 2-style 2">
-      <tableStyleElement dxfId="5" type="headerRow"/>
-      <tableStyleElement dxfId="6" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="7" size="0" type="wholeTable"/>
-    </tableStyle>
     <tableStyle count="4" pivot="0" name="MODELO DE LISTA DE COMPROBACION-style 3">
-      <tableStyleElement dxfId="8" type="headerRow"/>
-      <tableStyleElement dxfId="9" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="10" size="0" type="wholeTable"/>
-    </tableStyle>
-    <tableStyle count="4" pivot="0" name="MODELO LISTA DE COMPROBACION 2-style 3">
       <tableStyleElement dxfId="8" type="headerRow"/>
       <tableStyleElement dxfId="9" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
@@ -1825,7 +2138,7 @@
     <xdr:ext cx="4286250" cy="2143125"/>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 2"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1855,7 +2168,7 @@
     <xdr:ext cx="4286250" cy="2143125"/>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 3"/>
+        <xdr:cNvPr id="1" name="Chart 1"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1885,7 +2198,7 @@
     <xdr:ext cx="4286250" cy="2143125"/>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 2"/>
+        <xdr:cNvPr id="3" name="Chart 3"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1920,7 +2233,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A7:D16" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A7:D16" displayName="Table_1" name="Table_1" id="4">
   <tableColumns count="4">
     <tableColumn name="No." id="1"/>
     <tableColumn name="Pregunta" id="2"/>
@@ -1932,7 +2245,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A21:D26" displayName="Table_2" name="Table_2" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A21:D26" displayName="Table_2" name="Table_2" id="5">
   <tableColumns count="4">
     <tableColumn name="No." id="1"/>
     <tableColumn name="Pregunta" id="2"/>
@@ -1944,7 +2257,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A31:D34" displayName="Table_3" name="Table_3" id="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A31:D34" displayName="Table_3" name="Table_3" id="6">
   <tableColumns count="4">
     <tableColumn name="No." id="1"/>
     <tableColumn name="Pregunta" id="2"/>
@@ -1956,7 +2269,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A7:D16" displayName="Table" name="Table" id="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A7:D16" displayName="Table" name="Table" id="1">
   <tableColumns count="4">
     <tableColumn name="No." id="1"/>
     <tableColumn name="Pregunta" id="2"/>
@@ -1968,7 +2281,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A21:D26" displayName="Table_5" name="Table_5" id="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A21:D26" displayName="Table_5" name="Table_5" id="2">
   <tableColumns count="4">
     <tableColumn name="No." id="1"/>
     <tableColumn name="Pregunta" id="2"/>
@@ -1980,7 +2293,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A31:D34" displayName="Table_4" name="Table_4" id="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A31:D34" displayName="Table_4" name="Table_4" id="3">
   <tableColumns count="4">
     <tableColumn name="No." id="1"/>
     <tableColumn name="Pregunta" id="2"/>
@@ -1992,7 +2305,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A7:D16" displayName="Table_7" name="Table_7" id="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A7:D16" displayName="Table_7" name="Table_7" id="7">
   <tableColumns count="4">
     <tableColumn name="No." id="1"/>
     <tableColumn name="Pregunta" id="2"/>
@@ -2004,7 +2317,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A21:D26" displayName="Table_8" name="Table_8" id="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A21:D26" displayName="Table_8" name="Table_8" id="8">
   <tableColumns count="4">
     <tableColumn name="No." id="1"/>
     <tableColumn name="Pregunta" id="2"/>
@@ -2016,7 +2329,7 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A31:D34" displayName="Table_9" name="Table_9" id="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A31:D34" displayName="Table_9" name="Table_9" id="9">
   <tableColumns count="4">
     <tableColumn name="No." id="1"/>
     <tableColumn name="Pregunta" id="2"/>
@@ -2238,7 +2551,7 @@
     <col customWidth="1" hidden="1" min="8" max="8" width="4.71"/>
     <col customWidth="1" min="9" max="9" width="46.57"/>
     <col customWidth="1" min="10" max="10" width="9.86"/>
-    <col customWidth="1" min="11" max="11" width="52.29"/>
+    <col customWidth="1" min="11" max="11" width="44.29"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -2388,14 +2701,14 @@
       <c r="F11" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="25" t="s">
-        <v>17</v>
+      <c r="G11" s="19" t="s">
+        <v>11</v>
       </c>
       <c r="I11" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="J11" s="26" t="s">
-        <v>17</v>
+      <c r="J11" s="25" t="s">
+        <v>11</v>
       </c>
       <c r="K11" s="22" t="s">
         <v>16</v>
@@ -2406,25 +2719,25 @@
         <v>4.0</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="F12" s="27" t="s">
+      <c r="F12" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G12" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="I12" s="27" t="s">
+      <c r="I12" s="26" t="s">
         <v>20</v>
       </c>
       <c r="J12" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="K12" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="K12" s="26" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2439,19 +2752,19 @@
       <c r="E13" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="F13" s="27" t="s">
+      <c r="F13" s="26" t="s">
         <v>23</v>
       </c>
       <c r="G13" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="I13" s="27" t="s">
+      <c r="I13" s="26" t="s">
         <v>23</v>
       </c>
       <c r="J13" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="K13" s="27" t="s">
+      <c r="K13" s="26" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2466,19 +2779,19 @@
       <c r="E14" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="27" t="s">
+      <c r="F14" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="G14" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="I14" s="27" t="s">
+      <c r="G14" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="I14" s="26" t="s">
         <v>26</v>
       </c>
       <c r="J14" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="K14" s="27" t="s">
+      <c r="K14" s="26" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2493,19 +2806,19 @@
       <c r="E15" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="F15" s="27" t="s">
+      <c r="F15" s="26" t="s">
         <v>28</v>
       </c>
       <c r="G15" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="I15" s="27" t="s">
+      <c r="I15" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="J15" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="K15" s="27" t="s">
+      <c r="J15" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="K15" s="26" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2520,19 +2833,19 @@
       <c r="E16" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="F16" s="27" t="s">
+      <c r="F16" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="G16" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="I16" s="27" t="s">
+      <c r="G16" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="I16" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="J16" s="26" t="s">
+      <c r="J16" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="K16" s="27" t="s">
+      <c r="K16" s="26" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2547,19 +2860,19 @@
       <c r="E17" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="F17" s="28" t="s">
+      <c r="F17" s="29" t="s">
         <v>32</v>
       </c>
       <c r="G17" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="I17" s="28" t="s">
+      <c r="I17" s="29" t="s">
         <v>32</v>
       </c>
       <c r="J17" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="K17" s="28" t="s">
+      <c r="K17" s="29" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2574,19 +2887,19 @@
       <c r="E18" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="F18" s="27" t="s">
+      <c r="F18" s="26" t="s">
         <v>35</v>
       </c>
       <c r="G18" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="I18" s="27" t="s">
+      <c r="I18" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="J18" s="26" t="s">
+      <c r="J18" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="K18" s="27" t="s">
+      <c r="K18" s="26" t="s">
         <v>37</v>
       </c>
     </row>
@@ -2601,19 +2914,19 @@
       <c r="E19" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="F19" s="27" t="s">
+      <c r="F19" s="26" t="s">
         <v>39</v>
       </c>
       <c r="G19" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="I19" s="27" t="s">
+      <c r="I19" s="26" t="s">
         <v>40</v>
       </c>
       <c r="J19" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="K19" s="27" t="s">
+      <c r="K19" s="26" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2628,11 +2941,9 @@
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="C23" s="1"/>
-      <c r="E23" s="29"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="C24" s="1"/>
-      <c r="E24" s="19"/>
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="C25" s="1"/>
@@ -2641,43 +2952,191 @@
       <c r="C26" s="1"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
-      <c r="C27" s="1"/>
+      <c r="B27" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" s="10"/>
+      <c r="E27" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="28" ht="14.25" customHeight="1">
-      <c r="C28" s="1"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
     </row>
     <row r="29" ht="14.25" customHeight="1">
-      <c r="C29" s="1"/>
+      <c r="B29" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="7"/>
+      <c r="E29" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="20" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="30" ht="14.25" customHeight="1">
-      <c r="C30" s="1"/>
+      <c r="B30" s="17">
+        <v>2.0</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="7"/>
+      <c r="E30" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="22" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="31" ht="14.25" customHeight="1">
-      <c r="C31" s="1"/>
+      <c r="B31" s="17">
+        <v>3.0</v>
+      </c>
+      <c r="C31" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="7"/>
+      <c r="E31" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="22" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="32" ht="14.25" customHeight="1">
-      <c r="C32" s="1"/>
+      <c r="B32" s="17">
+        <v>4.0</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="D32" s="7"/>
+      <c r="E32" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="26" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="33" ht="14.25" customHeight="1">
-      <c r="C33" s="1"/>
+      <c r="B33" s="17">
+        <v>5.0</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="D33" s="7"/>
+      <c r="E33" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="26" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="34" ht="14.25" customHeight="1">
-      <c r="C34" s="1"/>
+      <c r="B34" s="17">
+        <v>6.0</v>
+      </c>
+      <c r="C34" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="D34" s="7"/>
+      <c r="E34" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="26" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="35" ht="14.25" customHeight="1">
-      <c r="C35" s="1"/>
+      <c r="B35" s="17">
+        <v>7.0</v>
+      </c>
+      <c r="C35" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D35" s="7"/>
+      <c r="E35" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="26" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="36" ht="14.25" customHeight="1">
-      <c r="C36" s="1"/>
+      <c r="B36" s="17">
+        <v>8.0</v>
+      </c>
+      <c r="C36" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="D36" s="7"/>
+      <c r="E36" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" s="26" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="37" ht="14.25" customHeight="1">
-      <c r="C37" s="1"/>
+      <c r="B37" s="17">
+        <v>9.0</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D37" s="7"/>
+      <c r="E37" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F37" s="29" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="38" ht="14.25" customHeight="1">
-      <c r="C38" s="1"/>
+      <c r="B38" s="17">
+        <v>10.0</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D38" s="7"/>
+      <c r="E38" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="26" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
-      <c r="C39" s="1"/>
+      <c r="B39" s="17">
+        <v>11.0</v>
+      </c>
+      <c r="C39" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D39" s="7"/>
+      <c r="E39" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39" s="26" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="40" ht="14.25" customHeight="1">
       <c r="C40" s="1"/>
@@ -2686,85 +3145,383 @@
       <c r="C41" s="1"/>
     </row>
     <row r="42" ht="14.25" customHeight="1">
-      <c r="C42" s="1"/>
+      <c r="B42" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D42" s="10"/>
+      <c r="E42" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F42" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="G42" s="30"/>
     </row>
     <row r="43" ht="14.25" customHeight="1">
-      <c r="C43" s="1"/>
+      <c r="B43" s="14"/>
+      <c r="C43" s="15"/>
+      <c r="D43" s="16"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
     </row>
     <row r="44" ht="14.25" customHeight="1">
-      <c r="C44" s="1"/>
+      <c r="B44" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="C44" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" s="7"/>
+      <c r="E44" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G44" s="30"/>
     </row>
     <row r="45" ht="14.25" customHeight="1">
-      <c r="C45" s="1"/>
+      <c r="B45" s="17">
+        <v>2.0</v>
+      </c>
+      <c r="C45" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" s="7"/>
+      <c r="E45" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F45" s="22" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="46" ht="14.25" customHeight="1">
-      <c r="C46" s="1"/>
+      <c r="B46" s="17">
+        <v>3.0</v>
+      </c>
+      <c r="C46" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" s="7"/>
+      <c r="E46" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F46" s="22" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="47" ht="14.25" customHeight="1">
-      <c r="C47" s="1"/>
+      <c r="B47" s="17">
+        <v>4.0</v>
+      </c>
+      <c r="C47" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="D47" s="7"/>
+      <c r="E47" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="F47" s="26" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="48" ht="14.25" customHeight="1">
-      <c r="C48" s="1"/>
+      <c r="B48" s="17">
+        <v>5.0</v>
+      </c>
+      <c r="C48" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="D48" s="7"/>
+      <c r="E48" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F48" s="26" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="49" ht="14.25" customHeight="1">
-      <c r="C49" s="1"/>
+      <c r="B49" s="17">
+        <v>6.0</v>
+      </c>
+      <c r="C49" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="D49" s="7"/>
+      <c r="E49" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F49" s="26" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="50" ht="14.25" customHeight="1">
-      <c r="C50" s="1"/>
+      <c r="B50" s="17">
+        <v>7.0</v>
+      </c>
+      <c r="C50" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D50" s="7"/>
+      <c r="E50" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F50" s="26" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="51" ht="14.25" customHeight="1">
-      <c r="C51" s="1"/>
+      <c r="B51" s="17">
+        <v>8.0</v>
+      </c>
+      <c r="C51" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="D51" s="7"/>
+      <c r="E51" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="F51" s="26" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="52" ht="14.25" customHeight="1">
-      <c r="C52" s="1"/>
+      <c r="B52" s="17">
+        <v>9.0</v>
+      </c>
+      <c r="C52" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D52" s="7"/>
+      <c r="E52" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F52" s="29" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="53" ht="14.25" customHeight="1">
-      <c r="C53" s="1"/>
+      <c r="B53" s="17">
+        <v>10.0</v>
+      </c>
+      <c r="C53" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D53" s="7"/>
+      <c r="E53" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F53" s="26" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="54" ht="14.25" customHeight="1">
-      <c r="C54" s="1"/>
+      <c r="B54" s="17">
+        <v>11.0</v>
+      </c>
+      <c r="C54" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D54" s="7"/>
+      <c r="E54" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F54" s="26" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="55" ht="14.25" customHeight="1">
       <c r="C55" s="1"/>
     </row>
     <row r="56" ht="14.25" customHeight="1">
-      <c r="C56" s="1"/>
+      <c r="B56" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D56" s="10"/>
+      <c r="E56" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F56" s="12" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="57" ht="14.25" customHeight="1">
-      <c r="C57" s="1"/>
+      <c r="B57" s="14"/>
+      <c r="C57" s="15"/>
+      <c r="D57" s="16"/>
+      <c r="E57" s="14"/>
+      <c r="F57" s="14"/>
     </row>
     <row r="58" ht="14.25" customHeight="1">
-      <c r="C58" s="1"/>
+      <c r="B58" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="C58" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D58" s="7"/>
+      <c r="E58" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F58" s="20" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="59" ht="14.25" customHeight="1">
-      <c r="C59" s="1"/>
+      <c r="B59" s="17">
+        <v>2.0</v>
+      </c>
+      <c r="C59" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D59" s="7"/>
+      <c r="E59" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F59" s="22" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="60" ht="14.25" customHeight="1">
-      <c r="C60" s="1"/>
+      <c r="B60" s="17">
+        <v>3.0</v>
+      </c>
+      <c r="C60" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D60" s="7"/>
+      <c r="E60" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="F60" s="22" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="61" ht="14.25" customHeight="1">
-      <c r="C61" s="1"/>
+      <c r="B61" s="17">
+        <v>4.0</v>
+      </c>
+      <c r="C61" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="D61" s="7"/>
+      <c r="E61" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="F61" s="26" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="62" ht="14.25" customHeight="1">
-      <c r="C62" s="1"/>
+      <c r="B62" s="17">
+        <v>5.0</v>
+      </c>
+      <c r="C62" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="D62" s="7"/>
+      <c r="E62" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F62" s="26" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="63" ht="14.25" customHeight="1">
-      <c r="C63" s="1"/>
+      <c r="B63" s="17">
+        <v>6.0</v>
+      </c>
+      <c r="C63" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="D63" s="7"/>
+      <c r="E63" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F63" s="26" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="64" ht="14.25" customHeight="1">
-      <c r="C64" s="1"/>
+      <c r="B64" s="17">
+        <v>7.0</v>
+      </c>
+      <c r="C64" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D64" s="7"/>
+      <c r="E64" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="F64" s="26" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="65" ht="14.25" customHeight="1">
-      <c r="C65" s="1"/>
+      <c r="B65" s="17">
+        <v>8.0</v>
+      </c>
+      <c r="C65" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="D65" s="7"/>
+      <c r="E65" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="F65" s="26" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="66" ht="14.25" customHeight="1">
-      <c r="C66" s="1"/>
+      <c r="B66" s="17">
+        <v>9.0</v>
+      </c>
+      <c r="C66" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D66" s="7"/>
+      <c r="E66" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F66" s="29" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="67" ht="14.25" customHeight="1">
-      <c r="C67" s="1"/>
+      <c r="B67" s="17">
+        <v>10.0</v>
+      </c>
+      <c r="C67" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D67" s="7"/>
+      <c r="E67" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="F67" s="26" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="68" ht="14.25" customHeight="1">
-      <c r="C68" s="1"/>
+      <c r="B68" s="17">
+        <v>11.0</v>
+      </c>
+      <c r="C68" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D68" s="7"/>
+      <c r="E68" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F68" s="26" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c r="C69" s="1"/>
@@ -4003,7 +4760,40 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="67">
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C42:D43"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="E56:E57"/>
+    <mergeCell ref="F56:F57"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="C56:D57"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="C63:D63"/>
     <mergeCell ref="G7:G8"/>
     <mergeCell ref="I7:I8"/>
     <mergeCell ref="J7:J8"/>
@@ -4015,10 +4805,6 @@
     <mergeCell ref="C7:D8"/>
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="F7:F8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C11:D11"/>
@@ -4026,6 +4812,22 @@
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="C27:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="F42:F43"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins bottom="0.7480314960629921" footer="0.0" header="0.0" left="0.47" right="0.7086614173228347" top="0.7480314960629921"/>
@@ -4053,303 +4855,305 @@
   </cols>
   <sheetData>
     <row r="1" ht="51.0" customHeight="1">
-      <c r="A1" s="30"/>
-      <c r="B1" s="31" t="s">
+      <c r="A1" s="31"/>
+      <c r="B1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-      <c r="W1" s="30"/>
-      <c r="X1" s="30"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="30"/>
+      <c r="C1" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="31"/>
+      <c r="Q1" s="31"/>
+      <c r="R1" s="31"/>
+      <c r="S1" s="31"/>
+      <c r="T1" s="31"/>
+      <c r="U1" s="31"/>
+      <c r="V1" s="31"/>
+      <c r="W1" s="31"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="31"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="34">
+      <c r="C2" s="35">
         <v>46227.0</v>
       </c>
     </row>
     <row r="3" ht="18.0" customHeight="1">
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="35" t="s">
-        <v>44</v>
+      <c r="C3" s="36" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="36" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1"/>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="36" t="s">
-        <v>46</v>
+      <c r="A6" s="37" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
-      <c r="A7" s="37" t="s">
-        <v>47</v>
-      </c>
-      <c r="B7" s="38" t="s">
+      <c r="A7" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="38" t="s">
+      <c r="B7" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="39" t="s">
+      <c r="C7" s="40" t="s">
         <v>50</v>
       </c>
+      <c r="D7" s="41" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="40">
+      <c r="A8" s="42">
         <v>1.0</v>
       </c>
-      <c r="B8" s="41" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" s="42" t="s">
+      <c r="B8" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="43"/>
+      <c r="C8" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="45"/>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="40">
+      <c r="A9" s="42">
         <v>2.0</v>
       </c>
-      <c r="B9" s="41" t="s">
+      <c r="B9" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="47" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" s="44"/>
+    </row>
+    <row r="10" ht="14.25" customHeight="1">
+      <c r="A10" s="42">
+        <v>3.0</v>
+      </c>
+      <c r="B10" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="42" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="B10" s="41" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" s="42" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="43"/>
+      <c r="D10" s="45"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="40">
+      <c r="A11" s="42">
         <v>4.0</v>
       </c>
-      <c r="B11" s="41" t="s">
-        <v>55</v>
-      </c>
-      <c r="C11" s="42" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="43"/>
+      <c r="B11" s="43" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="45"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="40">
+      <c r="A12" s="42">
         <v>5.0</v>
       </c>
-      <c r="B12" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" s="42" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" s="43"/>
+      <c r="B12" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="45"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="40">
+      <c r="A13" s="42">
         <v>6.0</v>
       </c>
-      <c r="B13" s="41" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" s="42" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="43"/>
+      <c r="B13" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="45"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="40">
+      <c r="A14" s="42">
         <v>7.0</v>
       </c>
-      <c r="B14" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" s="42" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" s="43"/>
+      <c r="B14" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="44"/>
+      <c r="D14" s="46" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="40">
+      <c r="A15" s="42">
         <v>8.0</v>
       </c>
-      <c r="B15" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" s="42" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" s="43"/>
+      <c r="B15" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" s="45"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="44">
+      <c r="A16" s="48">
         <v>9.0</v>
       </c>
-      <c r="B16" s="45" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" s="46" t="s">
-        <v>52</v>
+      <c r="B16" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="50"/>
+      <c r="D16" s="47" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="47" t="s">
-        <v>61</v>
+      <c r="A17" s="51" t="s">
+        <v>63</v>
       </c>
       <c r="C17" s="21">
         <f>COUNTA('MODELO LISTA DE COMPROBACION 1 '!$C$8:$C$16)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D17" s="21">
         <f>COUNTA('MODELO LISTA DE COMPROBACION 1 '!$D$8:$D$16)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="47" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18" s="48">
+      <c r="A18" s="51" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="52">
         <f t="shared" ref="C18:D18" si="1">C17/9</f>
-        <v>0.8888888889</v>
-      </c>
-      <c r="D18" s="48">
+        <v>0.7777777778</v>
+      </c>
+      <c r="D18" s="52">
         <f t="shared" si="1"/>
-        <v>0.1111111111</v>
+        <v>0.2222222222</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="47"/>
-      <c r="B19" s="47"/>
-      <c r="C19" s="48"/>
+      <c r="A19" s="51"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="52"/>
       <c r="D19" s="21"/>
     </row>
     <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="49" t="s">
+      <c r="A20" s="53" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" s="54"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+    </row>
+    <row r="21" ht="14.25" customHeight="1">
+      <c r="A21" s="55" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="56" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="57" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="58" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25" customHeight="1">
+      <c r="A22" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="B22" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" s="45"/>
+    </row>
+    <row r="23" ht="14.25" customHeight="1">
+      <c r="A23" s="42">
+        <v>2.0</v>
+      </c>
+      <c r="B23" s="43" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="45"/>
+    </row>
+    <row r="24" ht="14.25" customHeight="1">
+      <c r="A24" s="42">
+        <v>3.0</v>
+      </c>
+      <c r="B24" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24" s="45"/>
+    </row>
+    <row r="25" ht="14.25" customHeight="1">
+      <c r="A25" s="42">
+        <v>4.0</v>
+      </c>
+      <c r="B25" s="43" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25" s="45"/>
+    </row>
+    <row r="26" ht="14.25" customHeight="1">
+      <c r="A26" s="48">
+        <v>5.0</v>
+      </c>
+      <c r="B26" s="49" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="D26" s="59"/>
+    </row>
+    <row r="27" ht="14.25" customHeight="1">
+      <c r="A27" s="51" t="s">
         <v>63</v>
-      </c>
-      <c r="B20" s="50"/>
-      <c r="C20" s="50"/>
-      <c r="D20" s="50"/>
-    </row>
-    <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="51" t="s">
-        <v>47</v>
-      </c>
-      <c r="B21" s="52" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21" s="53" t="s">
-        <v>49</v>
-      </c>
-      <c r="D21" s="54" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="B22" s="41" t="s">
-        <v>64</v>
-      </c>
-      <c r="C22" s="46" t="s">
-        <v>52</v>
-      </c>
-      <c r="D22" s="43"/>
-    </row>
-    <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="B23" s="41" t="s">
-        <v>65</v>
-      </c>
-      <c r="C23" s="46" t="s">
-        <v>52</v>
-      </c>
-      <c r="D23" s="43"/>
-    </row>
-    <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="B24" s="41" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" s="46" t="s">
-        <v>52</v>
-      </c>
-      <c r="D24" s="43"/>
-    </row>
-    <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="B25" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C25" s="46" t="s">
-        <v>52</v>
-      </c>
-      <c r="D25" s="43"/>
-    </row>
-    <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="44">
-        <v>5.0</v>
-      </c>
-      <c r="B26" s="45" t="s">
-        <v>68</v>
-      </c>
-      <c r="C26" s="46" t="s">
-        <v>52</v>
-      </c>
-      <c r="D26" s="55"/>
-    </row>
-    <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="47" t="s">
-        <v>61</v>
       </c>
       <c r="C27" s="21">
         <f>COUNTA('MODELO LISTA DE COMPROBACION 1 '!$C$22:$C$26)</f>
@@ -4361,132 +5165,132 @@
       </c>
     </row>
     <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="47" t="s">
-        <v>62</v>
-      </c>
-      <c r="C28" s="48">
+      <c r="A28" s="51" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" s="52">
         <f t="shared" ref="C28:D28" si="2">C27/5</f>
         <v>1</v>
       </c>
-      <c r="D28" s="48">
+      <c r="D28" s="52">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="47"/>
-      <c r="B29" s="47"/>
-      <c r="C29" s="48"/>
+      <c r="A29" s="51"/>
+      <c r="B29" s="51"/>
+      <c r="C29" s="52"/>
       <c r="D29" s="21"/>
     </row>
     <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" s="36" t="s">
-        <v>69</v>
+      <c r="A30" s="37" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" s="51" t="s">
-        <v>47</v>
-      </c>
-      <c r="B31" s="52" t="s">
+      <c r="A31" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="C31" s="53" t="s">
+      <c r="B31" s="56" t="s">
         <v>49</v>
       </c>
-      <c r="D31" s="54" t="s">
+      <c r="C31" s="57" t="s">
         <v>50</v>
       </c>
+      <c r="D31" s="58" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="32" ht="14.25" customHeight="1">
-      <c r="A32" s="40">
+      <c r="A32" s="42">
         <v>1.0</v>
       </c>
-      <c r="B32" s="41" t="s">
-        <v>70</v>
-      </c>
-      <c r="C32" s="46" t="s">
-        <v>52</v>
-      </c>
-      <c r="D32" s="46"/>
+      <c r="B32" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" s="50"/>
+      <c r="D32" s="60" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="33" ht="14.25" customHeight="1">
-      <c r="A33" s="40">
+      <c r="A33" s="42">
         <v>2.0</v>
       </c>
-      <c r="B33" s="41" t="s">
-        <v>71</v>
-      </c>
-      <c r="C33" s="46" t="s">
-        <v>52</v>
-      </c>
-      <c r="D33" s="46"/>
+      <c r="B33" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="C33" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="D33" s="50"/>
     </row>
     <row r="34" ht="14.25" customHeight="1">
-      <c r="A34" s="44">
+      <c r="A34" s="48">
         <v>3.0</v>
       </c>
-      <c r="B34" s="45" t="s">
-        <v>72</v>
-      </c>
-      <c r="C34" s="46" t="s">
-        <v>52</v>
-      </c>
-      <c r="D34" s="46"/>
+      <c r="B34" s="49" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="D34" s="50"/>
     </row>
     <row r="35" ht="14.25" customHeight="1">
-      <c r="A35" s="47" t="s">
-        <v>61</v>
+      <c r="A35" s="51" t="s">
+        <v>63</v>
       </c>
       <c r="C35" s="21">
         <f>COUNTA('MODELO LISTA DE COMPROBACION 1 '!$C$32:$C$34)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D35" s="21">
         <f>COUNTA('MODELO LISTA DE COMPROBACION 1 '!$D$32:$D$34)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1">
-      <c r="A36" s="47" t="s">
-        <v>62</v>
-      </c>
-      <c r="C36" s="48">
+      <c r="A36" s="51" t="s">
+        <v>64</v>
+      </c>
+      <c r="C36" s="52">
         <f t="shared" ref="C36:D36" si="3">C35/3</f>
-        <v>1</v>
-      </c>
-      <c r="D36" s="48">
+        <v>0.6666666667</v>
+      </c>
+      <c r="D36" s="52">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.3333333333</v>
       </c>
     </row>
     <row r="37" ht="14.25" customHeight="1"/>
     <row r="38" ht="14.25" customHeight="1"/>
     <row r="39" ht="14.25" customHeight="1"/>
     <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="59" t="s">
+      <c r="A40" s="61" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="41" ht="30.0" customHeight="1">
+      <c r="B41" s="31" t="s">
         <v>77</v>
-      </c>
-    </row>
-    <row r="41" ht="30.0" customHeight="1">
-      <c r="B41" s="30" t="s">
-        <v>80</v>
       </c>
       <c r="C41" s="21">
         <v>89.0</v>
       </c>
     </row>
     <row r="42" ht="30.0" customHeight="1">
-      <c r="B42" s="30" t="s">
-        <v>63</v>
+      <c r="B42" s="31" t="s">
+        <v>65</v>
       </c>
       <c r="C42" s="21">
         <v>100.0</v>
       </c>
     </row>
     <row r="43" ht="30.0" customHeight="1">
-      <c r="B43" s="30" t="s">
-        <v>69</v>
+      <c r="B43" s="31" t="s">
+        <v>71</v>
       </c>
       <c r="C43" s="21">
         <v>100.0</v>
@@ -5538,441 +6342,442 @@
   </cols>
   <sheetData>
     <row r="1" ht="51.0" customHeight="1">
-      <c r="A1" s="30"/>
-      <c r="B1" s="31" t="s">
+      <c r="A1" s="31"/>
+      <c r="B1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-      <c r="W1" s="30"/>
-      <c r="X1" s="30"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="30"/>
+      <c r="C1" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="31"/>
+      <c r="Q1" s="31"/>
+      <c r="R1" s="31"/>
+      <c r="S1" s="31"/>
+      <c r="T1" s="31"/>
+      <c r="U1" s="31"/>
+      <c r="V1" s="31"/>
+      <c r="W1" s="31"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="31"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" ht="24.0" customHeight="1">
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="34">
-        <v>46227.0</v>
+      <c r="C2" s="35">
+        <v>46301.0</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="36" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="35" t="s">
-        <v>101</v>
+      <c r="C4" s="36" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1"/>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="36" t="s">
-        <v>46</v>
+      <c r="A6" s="37" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
-      <c r="A7" s="37" t="s">
-        <v>47</v>
-      </c>
-      <c r="B7" s="38" t="s">
+      <c r="A7" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="38" t="s">
+      <c r="B7" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="39" t="s">
+      <c r="C7" s="40" t="s">
         <v>50</v>
       </c>
+      <c r="D7" s="41" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="40">
+      <c r="A8" s="42">
         <v>1.0</v>
       </c>
-      <c r="B8" s="41" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" s="42" t="s">
+      <c r="B8" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="43"/>
+      <c r="C8" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="45"/>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="40">
+      <c r="A9" s="42">
         <v>2.0</v>
       </c>
-      <c r="B9" s="41" t="s">
+      <c r="B9" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="C9" s="43"/>
-      <c r="D9" s="42" t="s">
-        <v>52</v>
-      </c>
+      <c r="D9" s="44"/>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="40">
+      <c r="A10" s="42">
         <v>3.0</v>
       </c>
-      <c r="B10" s="41" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" s="42" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="43"/>
+      <c r="B10" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="45"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="40">
+      <c r="A11" s="42">
         <v>4.0</v>
       </c>
-      <c r="B11" s="41" t="s">
-        <v>55</v>
-      </c>
-      <c r="C11" s="42" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="43"/>
+      <c r="B11" s="43" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="45"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="40">
+      <c r="A12" s="42">
         <v>5.0</v>
       </c>
-      <c r="B12" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" s="42" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" s="43"/>
+      <c r="B12" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="45"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="40">
+      <c r="A13" s="42">
         <v>6.0</v>
       </c>
-      <c r="B13" s="41" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" s="42" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="43"/>
+      <c r="B13" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="45"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="40">
+      <c r="A14" s="42">
         <v>7.0</v>
       </c>
-      <c r="B14" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="42" t="s">
-        <v>52</v>
-      </c>
+      <c r="B14" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="47" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" s="44"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="40">
+      <c r="A15" s="42">
         <v>8.0</v>
       </c>
-      <c r="B15" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" s="42" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" s="43"/>
+      <c r="B15" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" s="45"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="44">
+      <c r="A16" s="48">
         <v>9.0</v>
       </c>
-      <c r="B16" s="45" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" s="46"/>
-      <c r="D16" s="46" t="s">
-        <v>52</v>
+      <c r="B16" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="50"/>
+      <c r="D16" s="50" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="47" t="s">
-        <v>61</v>
+      <c r="A17" s="51" t="s">
+        <v>63</v>
       </c>
       <c r="C17" s="21">
         <f>COUNTA('MODELO LISTA DE COMPROBACION 2'!$C$8:$C$16)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D17" s="21">
         <f>COUNTA('MODELO LISTA DE COMPROBACION 2'!$D$8:$D$16)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="47" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18" s="48">
+      <c r="A18" s="51" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="52">
         <f t="shared" ref="C18:D18" si="1">C17/9</f>
-        <v>0.6666666667</v>
-      </c>
-      <c r="D18" s="48">
+        <v>0.8888888889</v>
+      </c>
+      <c r="D18" s="52">
         <f t="shared" si="1"/>
-        <v>0.3333333333</v>
+        <v>0.1111111111</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="47"/>
-      <c r="B19" s="47"/>
-      <c r="C19" s="48"/>
+      <c r="A19" s="51"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="52"/>
       <c r="D19" s="21"/>
     </row>
     <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="49" t="s">
+      <c r="A20" s="53" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" s="54"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+    </row>
+    <row r="21" ht="14.25" customHeight="1">
+      <c r="A21" s="55" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="56" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="57" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="58" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25" customHeight="1">
+      <c r="A22" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="B22" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" s="45"/>
+    </row>
+    <row r="23" ht="14.25" customHeight="1">
+      <c r="A23" s="42">
+        <v>2.0</v>
+      </c>
+      <c r="B23" s="43" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="45"/>
+    </row>
+    <row r="24" ht="14.25" customHeight="1">
+      <c r="A24" s="42">
+        <v>3.0</v>
+      </c>
+      <c r="B24" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24" s="45"/>
+    </row>
+    <row r="25" ht="14.25" customHeight="1">
+      <c r="A25" s="42">
+        <v>4.0</v>
+      </c>
+      <c r="B25" s="43" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="50"/>
+      <c r="D25" s="46" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25" customHeight="1">
+      <c r="A26" s="48">
+        <v>5.0</v>
+      </c>
+      <c r="B26" s="49" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="D26" s="59"/>
+    </row>
+    <row r="27" ht="14.25" customHeight="1">
+      <c r="A27" s="51" t="s">
         <v>63</v>
-      </c>
-      <c r="B20" s="50"/>
-      <c r="C20" s="50"/>
-      <c r="D20" s="50"/>
-    </row>
-    <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="51" t="s">
-        <v>47</v>
-      </c>
-      <c r="B21" s="52" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21" s="53" t="s">
-        <v>49</v>
-      </c>
-      <c r="D21" s="54" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="B22" s="41" t="s">
-        <v>64</v>
-      </c>
-      <c r="C22" s="46" t="s">
-        <v>52</v>
-      </c>
-      <c r="D22" s="43"/>
-    </row>
-    <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="B23" s="41" t="s">
-        <v>65</v>
-      </c>
-      <c r="C23" s="46" t="s">
-        <v>52</v>
-      </c>
-      <c r="D23" s="43"/>
-    </row>
-    <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="B24" s="41" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" s="46" t="s">
-        <v>52</v>
-      </c>
-      <c r="D24" s="43"/>
-    </row>
-    <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="B25" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C25" s="46" t="s">
-        <v>52</v>
-      </c>
-      <c r="D25" s="43"/>
-    </row>
-    <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="44">
-        <v>5.0</v>
-      </c>
-      <c r="B26" s="45" t="s">
-        <v>68</v>
-      </c>
-      <c r="C26" s="46" t="s">
-        <v>52</v>
-      </c>
-      <c r="D26" s="55"/>
-    </row>
-    <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="47" t="s">
-        <v>61</v>
       </c>
       <c r="C27" s="21">
         <f>COUNTA('MODELO LISTA DE COMPROBACION 2'!$C$22:$C$26)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D27" s="21">
         <f>COUNTA('MODELO LISTA DE COMPROBACION 2'!$D$22:$D$26)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="47" t="s">
-        <v>62</v>
-      </c>
-      <c r="C28" s="48">
+      <c r="A28" s="51" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" s="52">
         <f t="shared" ref="C28:D28" si="2">C27/5</f>
-        <v>1</v>
-      </c>
-      <c r="D28" s="48">
+        <v>0.8</v>
+      </c>
+      <c r="D28" s="52">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="47"/>
-      <c r="B29" s="47"/>
-      <c r="C29" s="48"/>
+      <c r="A29" s="51"/>
+      <c r="B29" s="51"/>
+      <c r="C29" s="52"/>
       <c r="D29" s="21"/>
     </row>
     <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" s="36" t="s">
-        <v>69</v>
+      <c r="A30" s="37" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" s="51" t="s">
-        <v>47</v>
-      </c>
-      <c r="B31" s="52" t="s">
+      <c r="A31" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="C31" s="53" t="s">
+      <c r="B31" s="56" t="s">
         <v>49</v>
       </c>
-      <c r="D31" s="54" t="s">
+      <c r="C31" s="57" t="s">
         <v>50</v>
       </c>
+      <c r="D31" s="58" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="32" ht="14.25" customHeight="1">
-      <c r="A32" s="40">
+      <c r="A32" s="42">
         <v>1.0</v>
       </c>
-      <c r="B32" s="41" t="s">
-        <v>70</v>
-      </c>
-      <c r="C32" s="46" t="s">
-        <v>52</v>
-      </c>
-      <c r="D32" s="46"/>
+      <c r="B32" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" s="50"/>
+      <c r="D32" s="60" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="33" ht="14.25" customHeight="1">
-      <c r="A33" s="40">
+      <c r="A33" s="42">
         <v>2.0</v>
       </c>
-      <c r="B33" s="41" t="s">
-        <v>71</v>
-      </c>
-      <c r="C33" s="46" t="s">
-        <v>52</v>
-      </c>
-      <c r="D33" s="46"/>
+      <c r="B33" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="C33" s="50"/>
+      <c r="D33" s="60" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="34" ht="14.25" customHeight="1">
-      <c r="A34" s="44">
+      <c r="A34" s="48">
         <v>3.0</v>
       </c>
-      <c r="B34" s="45" t="s">
-        <v>72</v>
-      </c>
-      <c r="C34" s="46" t="s">
-        <v>52</v>
-      </c>
-      <c r="D34" s="46"/>
+      <c r="B34" s="49" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="D34" s="50"/>
     </row>
     <row r="35" ht="14.25" customHeight="1">
-      <c r="A35" s="47" t="s">
-        <v>61</v>
+      <c r="A35" s="51" t="s">
+        <v>63</v>
       </c>
       <c r="C35" s="21">
         <f>COUNTA('MODELO LISTA DE COMPROBACION 2'!$C$32:$C$34)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D35" s="21">
         <f>COUNTA('MODELO LISTA DE COMPROBACION 2'!$D$32:$D$34)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1">
-      <c r="A36" s="47" t="s">
-        <v>62</v>
-      </c>
-      <c r="C36" s="48">
+      <c r="A36" s="51" t="s">
+        <v>64</v>
+      </c>
+      <c r="C36" s="52">
         <f t="shared" ref="C36:D36" si="3">C35/3</f>
-        <v>1</v>
-      </c>
-      <c r="D36" s="48">
+        <v>0.3333333333</v>
+      </c>
+      <c r="D36" s="52">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.6666666667</v>
       </c>
     </row>
     <row r="37" ht="14.25" customHeight="1"/>
     <row r="38" ht="14.25" customHeight="1"/>
     <row r="39" ht="14.25" customHeight="1"/>
     <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="59" t="s">
+      <c r="A40" s="61" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="41" ht="30.0" customHeight="1">
+      <c r="B41" s="31" t="s">
         <v>77</v>
-      </c>
-    </row>
-    <row r="41" ht="30.0" customHeight="1">
-      <c r="B41" s="30" t="s">
-        <v>80</v>
       </c>
       <c r="C41" s="21">
         <v>89.0</v>
       </c>
     </row>
     <row r="42" ht="30.0" customHeight="1">
-      <c r="B42" s="30" t="s">
-        <v>63</v>
+      <c r="B42" s="31" t="s">
+        <v>65</v>
       </c>
       <c r="C42" s="21">
         <v>100.0</v>
       </c>
     </row>
     <row r="43" ht="30.0" customHeight="1">
-      <c r="B43" s="30" t="s">
-        <v>69</v>
+      <c r="B43" s="31" t="s">
+        <v>71</v>
       </c>
       <c r="C43" s="21">
         <v>100.0</v>
@@ -7017,198 +7822,198 @@
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="10.71"/>
-    <col customWidth="1" min="2" max="2" width="93.43"/>
+    <col customWidth="1" min="2" max="2" width="56.29"/>
     <col customWidth="1" min="3" max="3" width="16.14"/>
-    <col customWidth="1" min="4" max="4" width="53.57"/>
+    <col customWidth="1" min="4" max="4" width="21.14"/>
     <col customWidth="1" min="5" max="24" width="10.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="51.0" customHeight="1">
-      <c r="A1" s="30"/>
-      <c r="B1" s="31" t="s">
+      <c r="A1" s="31"/>
+      <c r="B1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="32" t="s">
+      <c r="C1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-      <c r="W1" s="30"/>
-      <c r="X1" s="30"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="30"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="31"/>
+      <c r="Q1" s="31"/>
+      <c r="R1" s="31"/>
+      <c r="S1" s="31"/>
+      <c r="T1" s="31"/>
+      <c r="U1" s="31"/>
+      <c r="V1" s="31"/>
+      <c r="W1" s="31"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="31"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" ht="30.0" customHeight="1">
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="34">
+      <c r="C2" s="35">
         <v>46227.0</v>
       </c>
     </row>
     <row r="3" ht="21.0" customHeight="1">
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="35" t="s">
-        <v>44</v>
+      <c r="C3" s="36" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="36" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1"/>
     <row r="6" ht="25.5" customHeight="1">
-      <c r="A6" s="36" t="s">
-        <v>46</v>
+      <c r="A6" s="37" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
-      <c r="A7" s="37" t="s">
-        <v>47</v>
-      </c>
-      <c r="B7" s="38" t="s">
+      <c r="A7" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="38" t="s">
+      <c r="B7" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="39" t="s">
+      <c r="C7" s="40" t="s">
         <v>50</v>
       </c>
+      <c r="D7" s="41" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="40">
+      <c r="A8" s="42">
         <v>1.0</v>
       </c>
-      <c r="B8" s="41" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" s="42" t="s">
+      <c r="B8" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="43"/>
+      <c r="C8" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="45"/>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="40">
+      <c r="A9" s="42">
         <v>2.0</v>
       </c>
-      <c r="B9" s="41" t="s">
+      <c r="B9" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="C9" s="42" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="43"/>
+      <c r="D9" s="45"/>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="40">
+      <c r="A10" s="42">
         <v>3.0</v>
       </c>
-      <c r="B10" s="41" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" s="42" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="43"/>
+      <c r="B10" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="45"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="40">
+      <c r="A11" s="42">
         <v>4.0</v>
       </c>
-      <c r="B11" s="41" t="s">
-        <v>55</v>
-      </c>
-      <c r="C11" s="42" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="43"/>
+      <c r="B11" s="43" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="45"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="40">
+      <c r="A12" s="42">
         <v>5.0</v>
       </c>
-      <c r="B12" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" s="42" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" s="43"/>
+      <c r="B12" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="45"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="40">
+      <c r="A13" s="42">
         <v>6.0</v>
       </c>
-      <c r="B13" s="41" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" s="42" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="43"/>
+      <c r="B13" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="45"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="40">
+      <c r="A14" s="42">
         <v>7.0</v>
       </c>
-      <c r="B14" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42" t="s">
-        <v>52</v>
+      <c r="B14" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="40">
+      <c r="A15" s="42">
         <v>8.0</v>
       </c>
-      <c r="B15" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" s="42" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" s="43"/>
+      <c r="B15" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" s="45"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="44">
+      <c r="A16" s="48">
         <v>9.0</v>
       </c>
-      <c r="B16" s="45" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" s="46"/>
-      <c r="D16" s="46" t="s">
-        <v>52</v>
+      <c r="B16" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="50"/>
+      <c r="D16" s="50" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="47" t="s">
-        <v>61</v>
+      <c r="A17" s="51" t="s">
+        <v>63</v>
       </c>
       <c r="C17" s="21">
         <f>COUNTA('MODELO DE LISTA DE COMPROBACION'!$C$8:$C$16)</f>
@@ -7220,246 +8025,246 @@
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="47" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18" s="48">
+      <c r="A18" s="51" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="52">
         <f t="shared" ref="C18:D18" si="1">C17/9</f>
         <v>0.7777777778</v>
       </c>
-      <c r="D18" s="48">
+      <c r="D18" s="52">
         <f t="shared" si="1"/>
         <v>0.2222222222</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="47"/>
-      <c r="B19" s="47"/>
-      <c r="C19" s="48"/>
+      <c r="A19" s="51"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="52"/>
       <c r="D19" s="21"/>
     </row>
     <row r="20" ht="29.25" customHeight="1">
-      <c r="A20" s="49" t="s">
+      <c r="A20" s="53" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" s="54"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+    </row>
+    <row r="21" ht="14.25" customHeight="1">
+      <c r="A21" s="55" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="56" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="57" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="58" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25" customHeight="1">
+      <c r="A22" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="B22" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" s="45"/>
+    </row>
+    <row r="23" ht="14.25" customHeight="1">
+      <c r="A23" s="42">
+        <v>2.0</v>
+      </c>
+      <c r="B23" s="43" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="50"/>
+      <c r="D23" s="46" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25" customHeight="1">
+      <c r="A24" s="42">
+        <v>3.0</v>
+      </c>
+      <c r="B24" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24" s="45"/>
+    </row>
+    <row r="25" ht="14.25" customHeight="1">
+      <c r="A25" s="42">
+        <v>4.0</v>
+      </c>
+      <c r="B25" s="43" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="50"/>
+      <c r="D25" s="46" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25" customHeight="1">
+      <c r="A26" s="48">
+        <v>5.0</v>
+      </c>
+      <c r="B26" s="49" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="D26" s="59"/>
+    </row>
+    <row r="27" ht="14.25" customHeight="1">
+      <c r="A27" s="51" t="s">
         <v>63</v>
-      </c>
-      <c r="B20" s="50"/>
-      <c r="C20" s="50"/>
-      <c r="D20" s="50"/>
-    </row>
-    <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="51" t="s">
-        <v>47</v>
-      </c>
-      <c r="B21" s="52" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21" s="53" t="s">
-        <v>49</v>
-      </c>
-      <c r="D21" s="54" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="B22" s="41" t="s">
-        <v>64</v>
-      </c>
-      <c r="C22" s="46" t="s">
-        <v>52</v>
-      </c>
-      <c r="D22" s="43"/>
-    </row>
-    <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="B23" s="41" t="s">
-        <v>65</v>
-      </c>
-      <c r="C23" s="46" t="s">
-        <v>52</v>
-      </c>
-      <c r="D23" s="43"/>
-    </row>
-    <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="B24" s="41" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" s="46" t="s">
-        <v>52</v>
-      </c>
-      <c r="D24" s="43"/>
-    </row>
-    <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="B25" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C25" s="46" t="s">
-        <v>52</v>
-      </c>
-      <c r="D25" s="43"/>
-    </row>
-    <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="44">
-        <v>5.0</v>
-      </c>
-      <c r="B26" s="45" t="s">
-        <v>68</v>
-      </c>
-      <c r="C26" s="46" t="s">
-        <v>52</v>
-      </c>
-      <c r="D26" s="55"/>
-    </row>
-    <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="47" t="s">
-        <v>61</v>
       </c>
       <c r="C27" s="21">
         <f>COUNTA('MODELO DE LISTA DE COMPROBACION'!$C$22:$C$26)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D27" s="21">
         <f>COUNTA('MODELO DE LISTA DE COMPROBACION'!$D$22:$D$26)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="47" t="s">
-        <v>62</v>
-      </c>
-      <c r="C28" s="48">
+      <c r="A28" s="51" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" s="52">
         <f t="shared" ref="C28:D28" si="2">C27/5</f>
-        <v>1</v>
-      </c>
-      <c r="D28" s="48">
+        <v>0.6</v>
+      </c>
+      <c r="D28" s="52">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="47"/>
-      <c r="B29" s="47"/>
-      <c r="C29" s="48"/>
+      <c r="A29" s="51"/>
+      <c r="B29" s="51"/>
+      <c r="C29" s="52"/>
       <c r="D29" s="21"/>
     </row>
     <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" s="36" t="s">
-        <v>69</v>
+      <c r="A30" s="37" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" s="51" t="s">
-        <v>47</v>
-      </c>
-      <c r="B31" s="52" t="s">
+      <c r="A31" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="C31" s="53" t="s">
+      <c r="B31" s="56" t="s">
         <v>49</v>
       </c>
-      <c r="D31" s="54" t="s">
+      <c r="C31" s="57" t="s">
         <v>50</v>
       </c>
+      <c r="D31" s="58" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="32" ht="14.25" customHeight="1">
-      <c r="A32" s="40">
+      <c r="A32" s="42">
         <v>1.0</v>
       </c>
-      <c r="B32" s="41" t="s">
-        <v>70</v>
-      </c>
-      <c r="C32" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="D32" s="46"/>
+      <c r="B32" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" s="60"/>
+      <c r="D32" s="60" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="33" ht="14.25" customHeight="1">
-      <c r="A33" s="40">
+      <c r="A33" s="42">
         <v>2.0</v>
       </c>
-      <c r="B33" s="41" t="s">
-        <v>71</v>
-      </c>
-      <c r="C33" s="46"/>
-      <c r="D33" s="46" t="s">
-        <v>52</v>
+      <c r="B33" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="C33" s="50"/>
+      <c r="D33" s="50" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="34" ht="14.25" customHeight="1">
-      <c r="A34" s="44">
+      <c r="A34" s="48">
         <v>3.0</v>
       </c>
-      <c r="B34" s="45" t="s">
-        <v>72</v>
-      </c>
-      <c r="C34" s="46" t="s">
-        <v>52</v>
-      </c>
-      <c r="D34" s="46"/>
+      <c r="B34" s="49" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="D34" s="50"/>
     </row>
     <row r="35" ht="14.25" customHeight="1">
-      <c r="A35" s="47" t="s">
-        <v>61</v>
+      <c r="A35" s="51" t="s">
+        <v>63</v>
       </c>
       <c r="C35" s="21">
         <f>COUNTA('MODELO DE LISTA DE COMPROBACION'!$C$32:$C$34)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35" s="21">
         <f>COUNTA('MODELO DE LISTA DE COMPROBACION'!$D$32:$D$34)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1">
-      <c r="A36" s="47" t="s">
-        <v>62</v>
-      </c>
-      <c r="C36" s="48">
+      <c r="A36" s="51" t="s">
+        <v>64</v>
+      </c>
+      <c r="C36" s="52">
         <f t="shared" ref="C36:D36" si="3">C35/3</f>
+        <v>0.3333333333</v>
+      </c>
+      <c r="D36" s="52">
+        <f t="shared" si="3"/>
         <v>0.6666666667</v>
-      </c>
-      <c r="D36" s="48">
-        <f t="shared" si="3"/>
-        <v>0.3333333333</v>
       </c>
     </row>
     <row r="37" ht="14.25" customHeight="1"/>
     <row r="38" ht="14.25" customHeight="1"/>
     <row r="39" ht="14.25" customHeight="1"/>
     <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="59" t="s">
+      <c r="A40" s="61" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="41" ht="30.0" customHeight="1">
+      <c r="B41" s="31" t="s">
         <v>77</v>
-      </c>
-    </row>
-    <row r="41" ht="30.0" customHeight="1">
-      <c r="B41" s="30" t="s">
-        <v>80</v>
       </c>
       <c r="C41" s="21">
         <v>78.0</v>
       </c>
     </row>
     <row r="42" ht="30.0" customHeight="1">
-      <c r="B42" s="30" t="s">
-        <v>63</v>
+      <c r="B42" s="31" t="s">
+        <v>65</v>
       </c>
       <c r="C42" s="21">
         <v>100.0</v>
       </c>
     </row>
     <row r="43" ht="30.0" customHeight="1">
-      <c r="B43" s="30" t="s">
-        <v>69</v>
+      <c r="B43" s="31" t="s">
+        <v>71</v>
       </c>
       <c r="C43" s="21">
         <v>33.0</v>
@@ -8509,36 +9314,49 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="56" t="s">
-        <v>73</v>
-      </c>
-      <c r="B1" s="56" t="s">
-        <v>74</v>
+      <c r="A1" s="62" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="62" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="57" t="s">
-        <v>75</v>
-      </c>
-      <c r="B2" s="58" t="s">
-        <v>76</v>
+      <c r="A2" s="63" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="63" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="B3" s="58" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="4" ht="14.25" customHeight="1"/>
+      <c r="A3" s="64" t="s">
+        <v>84</v>
+      </c>
+      <c r="B3" s="63" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25" customHeight="1">
+      <c r="A4" s="65" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="65" t="s">
+        <v>87</v>
+      </c>
+    </row>
     <row r="5" ht="14.25" customHeight="1"/>
-    <row r="6" ht="14.25" customHeight="1"/>
+    <row r="6" ht="14.25" customHeight="1">
+      <c r="B6" s="65"/>
+    </row>
     <row r="7" ht="14.25" customHeight="1"/>
-    <row r="8" ht="14.25" customHeight="1"/>
+    <row r="8" ht="14.25" customHeight="1">
+      <c r="B8" s="65"/>
+    </row>
     <row r="9" ht="14.25" customHeight="1"/>
-    <row r="10" ht="14.25" customHeight="1"/>
+    <row r="10" ht="14.25" customHeight="1">
+      <c r="B10" s="65"/>
+    </row>
     <row r="11" ht="14.25" customHeight="1"/>
     <row r="12" ht="14.25" customHeight="1"/>
     <row r="13" ht="14.25" customHeight="1"/>
@@ -9550,69 +10368,55 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="56" t="s">
-        <v>73</v>
-      </c>
-      <c r="B1" s="56" t="s">
-        <v>74</v>
+      <c r="A1" s="62" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="62" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="60" t="s">
-        <v>81</v>
-      </c>
-      <c r="B2" s="58" t="s">
-        <v>82</v>
+      <c r="A2" s="64" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" s="63" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="61" t="s">
-        <v>83</v>
-      </c>
-      <c r="B3" s="58" t="s">
-        <v>84</v>
+      <c r="A3" s="66" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="67" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="62" t="s">
-        <v>85</v>
-      </c>
-      <c r="B4" s="57" t="s">
-        <v>86</v>
+      <c r="A4" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="B4" s="63" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="B5" s="58" t="s">
-        <v>88</v>
+      <c r="A5" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5" s="63" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="62" t="s">
-        <v>89</v>
-      </c>
-      <c r="B6" s="58" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="62" t="s">
-        <v>91</v>
-      </c>
-      <c r="B7" s="58" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="62" t="s">
-        <v>85</v>
-      </c>
-      <c r="B8" s="57" t="s">
-        <v>86</v>
-      </c>
-    </row>
+      <c r="A6" s="66" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" s="63" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" customHeight="1"/>
+    <row r="8" ht="14.25" customHeight="1"/>
     <row r="9" ht="14.25" customHeight="1"/>
     <row r="10" ht="14.25" customHeight="1"/>
     <row r="11" ht="14.25" customHeight="1"/>
@@ -9821,8 +10625,8 @@
     <row r="214" ht="14.25" customHeight="1"/>
     <row r="215" ht="14.25" customHeight="1"/>
     <row r="216" ht="14.25" customHeight="1"/>
-    <row r="217" ht="14.25" customHeight="1"/>
-    <row r="218" ht="14.25" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
     <row r="219" ht="15.75" customHeight="1"/>
     <row r="220" ht="15.75" customHeight="1"/>
     <row r="221" ht="15.75" customHeight="1"/>
@@ -10601,8 +11405,6 @@
     <row r="994" ht="15.75" customHeight="1"/>
     <row r="995" ht="15.75" customHeight="1"/>
     <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
@@ -10618,49 +11420,45 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="54.14"/>
-    <col customWidth="1" min="2" max="2" width="57.29"/>
+    <col customWidth="1" min="1" max="1" width="120.86"/>
+    <col customWidth="1" min="2" max="2" width="105.29"/>
     <col customWidth="1" min="3" max="6" width="10.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="56" t="s">
-        <v>73</v>
-      </c>
-      <c r="B1" s="56" t="s">
-        <v>74</v>
-      </c>
+      <c r="A1" s="62"/>
+      <c r="B1" s="62"/>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="63" t="s">
-        <v>93</v>
-      </c>
-      <c r="B2" s="64" t="s">
-        <v>94</v>
+      <c r="A2" s="68" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" s="66" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="63" t="s">
-        <v>95</v>
-      </c>
-      <c r="B3" s="57" t="s">
-        <v>96</v>
+      <c r="A3" s="68" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" s="63" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="63" t="s">
-        <v>97</v>
-      </c>
-      <c r="B4" s="57" t="s">
-        <v>98</v>
+      <c r="A4" s="68" t="s">
+        <v>104</v>
+      </c>
+      <c r="B4" s="63" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="64" t="s">
-        <v>99</v>
-      </c>
-      <c r="B5" s="57" t="s">
-        <v>86</v>
+      <c r="A5" s="66" t="s">
+        <v>106</v>
+      </c>
+      <c r="B5" s="63" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1"/>
